--- a/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_aysen.xlsx
+++ b/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_aysen.xlsx
@@ -391,7 +391,7 @@
         <v>104.3432296713946</v>
       </c>
       <c r="C2">
-        <v>17.34327491634708</v>
+        <v>17.34327491634707</v>
       </c>
       <c r="D2">
         <v>64.56019190514752</v>
@@ -448,7 +448,7 @@
         <v>111.8155619596542</v>
       </c>
       <c r="C5">
-        <v>16.51070578905631</v>
+        <v>16.5107057890563</v>
       </c>
       <c r="D5">
         <v>65.02775574940523</v>
